--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129032743</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129011204</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129011201</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129032742</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129032743</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129011204</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129011201</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129032742</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129032743</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129011204</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129011201</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129032742</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129032743</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129011204</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129011201</v>
       </c>
       <c r="B5" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129032742</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129032743</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129011204</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129011201</v>
       </c>
       <c r="B5" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>129032742</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>129011203</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -782,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032743</v>
+        <v>129011204</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411123</v>
+        <v>412204</v>
       </c>
       <c r="R3" t="n">
-        <v>6781294</v>
+        <v>6781348</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +850,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,26 +877,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129011204</v>
+        <v>129032742</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412204</v>
+        <v>411132</v>
       </c>
       <c r="R4" t="n">
-        <v>6781348</v>
+        <v>6781293</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +957,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:04</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,44 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011201</v>
+        <v>129032743</v>
       </c>
       <c r="B5" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412187</v>
+        <v>411123</v>
       </c>
       <c r="R5" t="n">
-        <v>6781347</v>
+        <v>6781294</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,19 +1054,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,26 +1071,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032742</v>
+        <v>129032744</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1128,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411132</v>
+        <v>411196</v>
       </c>
       <c r="R6" t="n">
-        <v>6781293</v>
+        <v>6781276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,6 +1177,113 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129011201</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>412187</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6781347</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46348-2025 artfynd.xlsx
+++ b/artfynd/A 46348-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011203</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011204</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032744</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,8 +1314,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>